--- a/Copy of climate data 2007_2022.xlsx
+++ b/Copy of climate data 2007_2022.xlsx
@@ -13,49 +13,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="27">
   <si>
-    <t xml:space="preserve">year </t>
+    <t>year</t>
   </si>
   <si>
     <t>month</t>
   </si>
   <si>
-    <t>Average_Temp_C</t>
+    <t>average_temp_</t>
   </si>
   <si>
-    <t>Maximum_Temp_C</t>
+    <t>maximum_temp_c</t>
   </si>
   <si>
-    <t>Minimum_Temp_C</t>
+    <t>minimum_temp_c</t>
   </si>
   <si>
-    <t>Atmospheric_Pressure_Sea_level_hPa</t>
+    <t>atmospheric_pressure_sea_level_hPa</t>
   </si>
   <si>
-    <t>Average_Relative_Humidity_%</t>
+    <t>average_relative_humidity_percent</t>
   </si>
   <si>
-    <t>Total_Rainfall_mm</t>
+    <t>total_rainfall_mm</t>
   </si>
   <si>
-    <t>Average_Visibility_km</t>
+    <t>average_visibility_km</t>
   </si>
   <si>
-    <t>Average_Wind_Speed_kmh</t>
+    <t>average_wind_speed_kmh</t>
   </si>
   <si>
-    <t>Maximum_Sustained_Windspeed_kmh</t>
+    <t>maximum_sustained_windspeed_kmh</t>
   </si>
   <si>
-    <t>Total_Rain_days</t>
+    <t>total_rain_days</t>
   </si>
   <si>
-    <t>Snow_Indicator</t>
+    <t>snow_indicator</t>
   </si>
   <si>
-    <t>Storm_days</t>
+    <t>storm_days</t>
   </si>
   <si>
-    <t>Fog_days</t>
+    <t>fog_days</t>
   </si>
   <si>
     <t>Jan</t>
@@ -384,7 +384,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.13"/>
+    <col customWidth="1" min="1" max="1" width="4.75"/>
     <col customWidth="1" min="2" max="2" width="5.63"/>
     <col customWidth="1" min="3" max="3" width="8.5"/>
     <col customWidth="1" min="4" max="4" width="8.75"/>

--- a/Copy of climate data 2007_2022.xlsx
+++ b/Copy of climate data 2007_2022.xlsx
@@ -19,7 +19,7 @@
     <t>month</t>
   </si>
   <si>
-    <t>average_temp_</t>
+    <t>average_temp_c</t>
   </si>
   <si>
     <t>maximum_temp_c</t>

--- a/Copy of climate data 2007_2022.xlsx
+++ b/Copy of climate data 2007_2022.xlsx
@@ -4444,6 +4444,9 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B87" s="1" t="s">
         <v>16</v>
       </c>
@@ -4488,6 +4491,9 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B88" s="1" t="s">
         <v>17</v>
       </c>
@@ -4532,6 +4538,9 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B89" s="1" t="s">
         <v>18</v>
       </c>
@@ -4576,6 +4585,9 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B90" s="1" t="s">
         <v>19</v>
       </c>
@@ -4620,6 +4632,9 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B91" s="1" t="s">
         <v>20</v>
       </c>
@@ -4664,6 +4679,9 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B92" s="1" t="s">
         <v>21</v>
       </c>
@@ -4708,6 +4726,9 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B93" s="1" t="s">
         <v>22</v>
       </c>
@@ -4752,6 +4773,9 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B94" s="1" t="s">
         <v>23</v>
       </c>
@@ -4796,6 +4820,9 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B95" s="1" t="s">
         <v>24</v>
       </c>
@@ -4840,6 +4867,9 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B96" s="1" t="s">
         <v>25</v>
       </c>
@@ -4884,6 +4914,9 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" s="1">
+        <v>2014.0</v>
+      </c>
       <c r="B97" s="1" t="s">
         <v>26</v>
       </c>
@@ -4975,6 +5008,9 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B99" s="1" t="s">
         <v>16</v>
       </c>
@@ -5019,6 +5055,9 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B100" s="1" t="s">
         <v>17</v>
       </c>
@@ -5063,6 +5102,9 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B101" s="1" t="s">
         <v>18</v>
       </c>
@@ -5107,6 +5149,9 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B102" s="1" t="s">
         <v>19</v>
       </c>
@@ -5151,6 +5196,9 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B103" s="1" t="s">
         <v>20</v>
       </c>
@@ -5195,6 +5243,9 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B104" s="1" t="s">
         <v>21</v>
       </c>
@@ -5207,6 +5258,9 @@
       <c r="E104" s="1">
         <v>25.8</v>
       </c>
+      <c r="F104" s="1">
+        <v>1014.4</v>
+      </c>
       <c r="G104" s="1">
         <v>77.8</v>
       </c>
@@ -5236,6 +5290,9 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B105" s="1" t="s">
         <v>22</v>
       </c>
@@ -5248,11 +5305,14 @@
       <c r="E105" s="1">
         <v>26.2</v>
       </c>
+      <c r="F105" s="1">
+        <v>1013.3</v>
+      </c>
       <c r="G105" s="1">
         <v>77.8</v>
       </c>
       <c r="H105" s="1">
-        <v>0.0</v>
+        <v>102.4</v>
       </c>
       <c r="I105" s="1">
         <v>10.0</v>
@@ -5277,6 +5337,9 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B106" s="1" t="s">
         <v>23</v>
       </c>
@@ -5289,11 +5352,14 @@
       <c r="E106" s="1">
         <v>26.5</v>
       </c>
+      <c r="F106" s="1">
+        <v>1012.5</v>
+      </c>
       <c r="G106" s="1">
         <v>78.2</v>
       </c>
       <c r="H106" s="1">
-        <v>0.0</v>
+        <v>98.6</v>
       </c>
       <c r="I106" s="1">
         <v>9.9</v>
@@ -5318,6 +5384,9 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B107" s="1" t="s">
         <v>24</v>
       </c>
@@ -5330,11 +5399,14 @@
       <c r="E107" s="1">
         <v>26.8</v>
       </c>
+      <c r="F107" s="1">
+        <v>1011.5</v>
+      </c>
       <c r="G107" s="1">
         <v>78.2</v>
       </c>
       <c r="H107" s="1">
-        <v>0.0</v>
+        <v>124.2</v>
       </c>
       <c r="I107" s="1">
         <v>10.0</v>
@@ -5359,6 +5431,9 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B108" s="1" t="s">
         <v>25</v>
       </c>
@@ -5371,11 +5446,14 @@
       <c r="E108" s="1">
         <v>25.9</v>
       </c>
+      <c r="F108" s="1">
+        <v>1011.2</v>
+      </c>
       <c r="G108" s="1">
         <v>78.6</v>
       </c>
       <c r="H108" s="1">
-        <v>0.0</v>
+        <v>134.0</v>
       </c>
       <c r="I108" s="1">
         <v>10.0</v>
@@ -5400,6 +5478,9 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" s="1">
+        <v>2015.0</v>
+      </c>
       <c r="B109" s="1" t="s">
         <v>26</v>
       </c>
@@ -5412,11 +5493,14 @@
       <c r="E109" s="1">
         <v>25.4</v>
       </c>
+      <c r="F109" s="1">
+        <v>1013.0</v>
+      </c>
       <c r="G109" s="1">
         <v>76.8</v>
       </c>
       <c r="H109" s="1">
-        <v>0.0</v>
+        <v>72.5</v>
       </c>
       <c r="I109" s="1">
         <v>9.9</v>
@@ -5456,12 +5540,14 @@
       <c r="E110" s="3">
         <v>24.3</v>
       </c>
-      <c r="F110" s="3"/>
+      <c r="F110" s="1">
+        <v>1014.3</v>
+      </c>
       <c r="G110" s="3">
         <v>75.8</v>
       </c>
-      <c r="H110" s="3">
-        <v>0.0</v>
+      <c r="H110" s="1">
+        <v>56.8</v>
       </c>
       <c r="I110" s="3">
         <v>9.9</v>
@@ -5486,7 +5572,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4"/>
+      <c r="A111" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B111" s="4" t="s">
         <v>16</v>
       </c>
@@ -5531,7 +5619,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4"/>
+      <c r="A112" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B112" s="4" t="s">
         <v>17</v>
       </c>
@@ -5576,7 +5666,9 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4"/>
+      <c r="A113" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B113" s="4" t="s">
         <v>18</v>
       </c>
@@ -5621,7 +5713,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4"/>
+      <c r="A114" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B114" s="4" t="s">
         <v>19</v>
       </c>
@@ -5666,7 +5760,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4"/>
+      <c r="A115" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B115" s="4" t="s">
         <v>20</v>
       </c>
@@ -5711,7 +5807,9 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4"/>
+      <c r="A116" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B116" s="4" t="s">
         <v>21</v>
       </c>
@@ -5756,7 +5854,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4"/>
+      <c r="A117" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B117" s="4" t="s">
         <v>22</v>
       </c>
@@ -5801,7 +5901,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4"/>
+      <c r="A118" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B118" s="4" t="s">
         <v>23</v>
       </c>
@@ -5846,7 +5948,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4"/>
+      <c r="A119" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B119" s="4" t="s">
         <v>24</v>
       </c>
@@ -5891,7 +5995,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4"/>
+      <c r="A120" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B120" s="4" t="s">
         <v>25</v>
       </c>
@@ -5936,7 +6042,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4"/>
+      <c r="A121" s="3">
+        <v>2016.0</v>
+      </c>
       <c r="B121" s="4" t="s">
         <v>26</v>
       </c>
@@ -6028,6 +6136,9 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B123" s="1" t="s">
         <v>16</v>
       </c>
@@ -6072,6 +6183,9 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B124" s="1" t="s">
         <v>17</v>
       </c>
@@ -6116,6 +6230,9 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B125" s="1" t="s">
         <v>18</v>
       </c>
@@ -6160,6 +6277,9 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B126" s="1" t="s">
         <v>19</v>
       </c>
@@ -6204,6 +6324,9 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B127" s="1" t="s">
         <v>20</v>
       </c>
@@ -6248,6 +6371,9 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B128" s="1" t="s">
         <v>21</v>
       </c>
@@ -6292,6 +6418,9 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B129" s="1" t="s">
         <v>22</v>
       </c>
@@ -6336,6 +6465,9 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B130" s="1" t="s">
         <v>23</v>
       </c>
@@ -6380,6 +6512,9 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B131" s="1" t="s">
         <v>24</v>
       </c>
@@ -6424,6 +6559,9 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B132" s="1" t="s">
         <v>25</v>
       </c>
@@ -6468,6 +6606,9 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" s="1">
+        <v>2017.0</v>
+      </c>
       <c r="B133" s="1" t="s">
         <v>26</v>
       </c>
@@ -6559,6 +6700,9 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B135" s="1" t="s">
         <v>16</v>
       </c>
@@ -6603,6 +6747,9 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B136" s="1" t="s">
         <v>17</v>
       </c>
@@ -6647,6 +6794,9 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B137" s="1" t="s">
         <v>18</v>
       </c>
@@ -6691,6 +6841,9 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B138" s="1" t="s">
         <v>19</v>
       </c>
@@ -6735,6 +6888,9 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B139" s="1" t="s">
         <v>20</v>
       </c>
@@ -6779,6 +6935,9 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B140" s="1" t="s">
         <v>21</v>
       </c>
@@ -6823,6 +6982,9 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B141" s="1" t="s">
         <v>22</v>
       </c>
@@ -6867,7 +7029,9 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1"/>
+      <c r="A142" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B142" s="1" t="s">
         <v>23</v>
       </c>
@@ -6912,6 +7076,9 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B143" s="1" t="s">
         <v>24</v>
       </c>
@@ -6956,6 +7123,9 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B144" s="1" t="s">
         <v>25</v>
       </c>
@@ -7000,6 +7170,9 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" s="1">
+        <v>2018.0</v>
+      </c>
       <c r="B145" s="1" t="s">
         <v>26</v>
       </c>
@@ -7091,6 +7264,9 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B147" s="1" t="s">
         <v>16</v>
       </c>
@@ -7135,6 +7311,9 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B148" s="1" t="s">
         <v>17</v>
       </c>
@@ -7179,6 +7358,9 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B149" s="1" t="s">
         <v>18</v>
       </c>
@@ -7223,6 +7405,9 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B150" s="1" t="s">
         <v>19</v>
       </c>
@@ -7235,6 +7420,9 @@
       <c r="E150" s="1">
         <v>26.0</v>
       </c>
+      <c r="F150" s="1">
+        <v>1014.2</v>
+      </c>
       <c r="G150" s="1">
         <v>72.3</v>
       </c>
@@ -7264,6 +7452,9 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B151" s="1" t="s">
         <v>20</v>
       </c>
@@ -7308,6 +7499,9 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B152" s="1" t="s">
         <v>21</v>
       </c>
@@ -7352,6 +7546,9 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B153" s="1" t="s">
         <v>22</v>
       </c>
@@ -7396,6 +7593,9 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B154" s="1" t="s">
         <v>23</v>
       </c>
@@ -7440,6 +7640,9 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B155" s="1" t="s">
         <v>24</v>
       </c>
@@ -7484,6 +7687,9 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B156" s="1" t="s">
         <v>25</v>
       </c>
@@ -7528,6 +7734,9 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" s="1">
+        <v>2019.0</v>
+      </c>
       <c r="B157" s="1" t="s">
         <v>26</v>
       </c>
@@ -7619,6 +7828,9 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B159" s="1" t="s">
         <v>16</v>
       </c>
@@ -7663,6 +7875,9 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B160" s="1" t="s">
         <v>17</v>
       </c>
@@ -7707,6 +7922,9 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B161" s="1" t="s">
         <v>18</v>
       </c>
@@ -7751,6 +7969,9 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B162" s="1" t="s">
         <v>19</v>
       </c>
@@ -7795,6 +8016,9 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B163" s="1" t="s">
         <v>20</v>
       </c>
@@ -7839,6 +8063,9 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B164" s="1" t="s">
         <v>21</v>
       </c>
@@ -7883,6 +8110,9 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B165" s="1" t="s">
         <v>22</v>
       </c>
@@ -7927,6 +8157,9 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B166" s="1" t="s">
         <v>23</v>
       </c>
@@ -7971,6 +8204,9 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B167" s="1" t="s">
         <v>24</v>
       </c>
@@ -8015,6 +8251,9 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B168" s="1" t="s">
         <v>25</v>
       </c>
@@ -8059,6 +8298,9 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" s="1">
+        <v>2020.0</v>
+      </c>
       <c r="B169" s="1" t="s">
         <v>26</v>
       </c>
@@ -8150,6 +8392,9 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B171" s="1" t="s">
         <v>16</v>
       </c>
@@ -8194,6 +8439,9 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B172" s="1" t="s">
         <v>17</v>
       </c>
@@ -8238,6 +8486,9 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B173" s="1" t="s">
         <v>18</v>
       </c>
@@ -8282,6 +8533,9 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B174" s="1" t="s">
         <v>19</v>
       </c>
@@ -8326,6 +8580,9 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B175" s="1" t="s">
         <v>20</v>
       </c>
@@ -8370,6 +8627,9 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B176" s="1" t="s">
         <v>21</v>
       </c>
@@ -8414,6 +8674,9 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B177" s="1" t="s">
         <v>22</v>
       </c>
@@ -8458,6 +8721,9 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B178" s="1" t="s">
         <v>23</v>
       </c>
@@ -8502,6 +8768,9 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B179" s="1" t="s">
         <v>24</v>
       </c>
@@ -8546,6 +8815,9 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B180" s="1" t="s">
         <v>25</v>
       </c>
@@ -8590,6 +8862,9 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" s="1">
+        <v>2021.0</v>
+      </c>
       <c r="B181" s="1" t="s">
         <v>26</v>
       </c>
@@ -8681,6 +8956,9 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B183" s="1" t="s">
         <v>16</v>
       </c>
@@ -8725,6 +9003,9 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B184" s="1" t="s">
         <v>17</v>
       </c>
@@ -8769,6 +9050,9 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B185" s="1" t="s">
         <v>18</v>
       </c>
@@ -8788,7 +9072,7 @@
         <v>73.7</v>
       </c>
       <c r="H185" s="1">
-        <v>0.0</v>
+        <v>24.1</v>
       </c>
       <c r="I185" s="1">
         <v>10.3</v>
@@ -8813,6 +9097,9 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B186" s="1" t="s">
         <v>19</v>
       </c>
@@ -8825,11 +9112,14 @@
       <c r="E186" s="1">
         <v>26.1</v>
       </c>
+      <c r="F186" s="1">
+        <v>1014.2</v>
+      </c>
       <c r="G186" s="1">
         <v>75.5</v>
       </c>
       <c r="H186" s="1">
-        <v>0.0</v>
+        <v>18.3</v>
       </c>
       <c r="I186" s="1">
         <v>10.0</v>
@@ -8854,6 +9144,9 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B187" s="1" t="s">
         <v>20</v>
       </c>
@@ -8866,11 +9159,14 @@
       <c r="E187" s="1">
         <v>26.0</v>
       </c>
+      <c r="F187" s="1">
+        <v>1014.8</v>
+      </c>
       <c r="G187" s="1">
         <v>77.3</v>
       </c>
       <c r="H187" s="1">
-        <v>0.0</v>
+        <v>102.8</v>
       </c>
       <c r="I187" s="1">
         <v>9.9</v>
@@ -8895,6 +9191,9 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B188" s="1" t="s">
         <v>21</v>
       </c>
@@ -8907,11 +9206,14 @@
       <c r="E188" s="1">
         <v>26.1</v>
       </c>
+      <c r="F188" s="1">
+        <v>1014.4</v>
+      </c>
       <c r="G188" s="1">
         <v>77.3</v>
       </c>
       <c r="H188" s="1">
-        <v>0.0</v>
+        <v>145.8</v>
       </c>
       <c r="I188" s="1">
         <v>9.9</v>
@@ -8936,6 +9238,9 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B189" s="1" t="s">
         <v>22</v>
       </c>
@@ -8948,11 +9253,14 @@
       <c r="E189" s="1">
         <v>25.9</v>
       </c>
+      <c r="F189" s="1">
+        <v>1013.3</v>
+      </c>
       <c r="G189" s="1">
         <v>77.9</v>
       </c>
       <c r="H189" s="1">
-        <v>0.0</v>
+        <v>168.3</v>
       </c>
       <c r="I189" s="1">
         <v>9.9</v>
@@ -8977,6 +9285,9 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B190" s="1" t="s">
         <v>23</v>
       </c>
@@ -8989,11 +9300,14 @@
       <c r="E190" s="1">
         <v>25.7</v>
       </c>
+      <c r="F190" s="1">
+        <v>1012.5</v>
+      </c>
       <c r="G190" s="1">
         <v>78.9</v>
       </c>
       <c r="H190" s="1">
-        <v>0.0</v>
+        <v>192.1</v>
       </c>
       <c r="I190" s="1">
         <v>9.9</v>
@@ -9018,6 +9332,9 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B191" s="1" t="s">
         <v>24</v>
       </c>
@@ -9062,6 +9379,9 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B192" s="1" t="s">
         <v>25</v>
       </c>
@@ -9106,6 +9426,9 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" s="1">
+        <v>2022.0</v>
+      </c>
       <c r="B193" s="1" t="s">
         <v>26</v>
       </c>
